--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="313">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,6 +455,189 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>DeviceUseStatement.extension:performer</t>
+  </si>
+  <si>
+    <t>performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Dispensateur: référence au professionnel de santé ou à l'organisation ayant initié ou dispensé le dispositif</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:type.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:type.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:actor.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:actor.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension:performer.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
     <t>DeviceUseStatement.extension:notCovered</t>
   </si>
   <si>
@@ -471,10 +654,6 @@
     <t>Extension permettant d'indiquer si le traitement est non remboursable.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DeviceUseStatement.modifierExtension</t>
   </si>
   <si>
@@ -505,8 +684,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de la fourniture du DM
-Sous la forme UID (UUID ou OID).</t>
+    <t>Identifiant de la fourniture du DM.</t>
   </si>
   <si>
     <t>An external identifier for this statement such as an IRI.</t>
@@ -564,9 +742,6 @@
 This element is labeled as a modifier because the status contains the codes that mark the statement as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A coded concept indicating the current status of the Device Usage.</t>
   </si>
   <si>
@@ -671,7 +846,7 @@
 </t>
   </si>
   <si>
-    <t>Dispensateur</t>
+    <t>Who made the statement</t>
   </si>
   <si>
     <t>Who reported the device was being used by the patient.</t>
@@ -681,274 +856,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer</t>
-  </si>
-  <si>
-    <t>performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Dispensateur: référence au professionnel de santé ou à l'organisation ayant initié ou dispensé le dispositif</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:type.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.extension.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:type.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:type.url</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>PRF</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:actor.id</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:actor.url</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
-</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.url</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension:performer.value[x]</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.source.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>DeviceUseStatement.device</t>
@@ -1403,11 +1310,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.30859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.55859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2623,43 +2530,39 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -2707,42 +2610,42 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>132</v>
-      </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2750,28 +2653,28 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2810,19 +2713,19 @@
         <v>78</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2834,16 +2737,16 @@
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -2854,21 +2757,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
@@ -2877,21 +2782,19 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
@@ -2939,7 +2842,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2951,10 +2854,10 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
@@ -2963,18 +2866,18 @@
         <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2982,7 +2885,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -2991,23 +2894,21 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3032,13 +2933,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3056,10 +2957,10 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>89</v>
@@ -3068,30 +2969,30 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>180</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3099,10 +3000,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
@@ -3111,16 +3012,16 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3159,40 +3060,40 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3203,10 +3104,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3214,10 +3115,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3226,19 +3127,19 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3246,7 +3147,7 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>78</v>
@@ -3288,19 +3189,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3315,15 +3216,15 @@
         <v>78</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3343,16 +3244,16 @@
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3364,7 +3265,7 @@
         <v>78</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>78</v>
@@ -3379,13 +3280,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3403,7 +3302,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3418,29 +3317,31 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3458,16 +3359,16 @@
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3518,28 +3419,28 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3548,12 +3449,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3567,22 +3468,22 @@
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3633,7 +3534,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3645,30 +3546,30 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3679,7 +3580,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
@@ -3691,13 +3592,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3736,31 +3637,31 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3775,26 +3676,26 @@
         <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3806,16 +3707,16 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3823,7 +3724,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>78</v>
@@ -3853,31 +3754,31 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -3892,19 +3793,17 @@
         <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>217</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>78</v>
       </c>
@@ -3925,13 +3824,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3982,19 +3881,19 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
@@ -4009,23 +3908,25 @@
         <v>78</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4040,13 +3941,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4097,19 +3998,19 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4124,15 +4025,15 @@
         <v>78</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4140,10 +4041,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4155,13 +4056,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4200,31 +4101,31 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4239,28 +4140,26 @@
         <v>78</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4317,19 +4216,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4361,10 +4260,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>166</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4372,7 +4271,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>89</v>
@@ -4387,22 +4286,24 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>213</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>78</v>
@@ -4444,10 +4345,10 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>89</v>
@@ -4471,15 +4372,15 @@
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>217</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4490,7 +4391,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4502,13 +4403,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4547,31 +4448,31 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4586,15 +4487,15 @@
         <v>78</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4620,13 +4521,13 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>167</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4634,7 +4535,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>78</v>
@@ -4676,7 +4577,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>89</v>
@@ -4708,10 +4609,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4722,7 +4623,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4734,13 +4635,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>248</v>
+        <v>174</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4752,7 +4653,7 @@
         <v>78</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>78</v>
@@ -4767,11 +4668,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -4789,7 +4692,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4821,13 +4724,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>78</v>
@@ -4849,13 +4752,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4906,7 +4809,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4915,7 +4818,7 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>140</v>
@@ -4938,42 +4841,46 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5021,19 +4928,19 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -5048,15 +4955,15 @@
         <v>78</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>217</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5067,7 +4974,7 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
@@ -5076,16 +4983,16 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5124,19 +5031,19 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5148,16 +5055,16 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5168,21 +5075,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -5191,27 +5098,27 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -5253,22 +5160,22 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
@@ -5277,18 +5184,18 @@
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>132</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5296,7 +5203,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -5305,21 +5212,23 @@
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5344,13 +5253,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5368,10 +5277,10 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>89</v>
@@ -5383,31 +5292,29 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5425,16 +5332,16 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>136</v>
+        <v>241</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5485,28 +5392,28 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5517,10 +5424,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5531,7 +5438,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5540,18 +5447,20 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5600,19 +5509,19 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -5627,15 +5536,15 @@
         <v>78</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5646,7 +5555,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -5655,16 +5564,16 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>135</v>
+        <v>252</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5703,40 +5612,40 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5747,10 +5656,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5758,7 +5667,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -5770,104 +5679,102 @@
         <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="S38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AM38" t="s" s="2">
-        <v>78</v>
+        <v>262</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5887,16 +5794,16 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5947,7 +5854,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5962,27 +5869,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5996,76 +5903,74 @@
         <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="S40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>89</v>
       </c>
@@ -6076,30 +5981,30 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6110,7 +6015,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -6119,16 +6024,16 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>272</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6179,13 +6084,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6194,27 +6099,27 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6225,10 +6130,10 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -6237,17 +6142,15 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6284,56 +6187,56 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>132</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6345,7 +6248,7 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6354,17 +6257,15 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>290</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6389,13 +6290,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>285</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6413,13 +6314,13 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
@@ -6428,29 +6329,31 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>132</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6462,7 +6365,7 @@
         <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6471,17 +6374,15 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>155</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6530,13 +6431,13 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -6545,29 +6446,31 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
@@ -6579,7 +6482,7 @@
         <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
@@ -6588,17 +6491,15 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6647,13 +6548,13 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
@@ -6662,27 +6563,27 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>132</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6690,13 +6591,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -6705,7 +6606,7 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>299</v>
+        <v>186</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>300</v>
@@ -6714,7 +6615,9 @@
         <v>301</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6738,13 +6641,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -6762,10 +6665,10 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>89</v>
@@ -6777,27 +6680,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6817,16 +6720,16 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6877,7 +6780,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6895,716 +6798,20 @@
         <v>306</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AC48" s="2"/>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO53">
+  <autoFilter ref="A1:AO47">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7614,7 +6821,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
